--- a/data/raw/benv_exports/brucellosi_2026_italia.xlsx
+++ b/data/raw/benv_exports/brucellosi_2026_italia.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,7 +449,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>83753</v>
+        <v>83918</v>
       </c>
       <c r="B3" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -458,13 +458,13 @@
         <v>E</v>
       </c>
       <c r="D3" t="str">
-        <v>08/04/2026</v>
+        <v>26/05/2026</v>
       </c>
       <c r="E3" t="str">
-        <v>09/03/2026</v>
+        <v>16/03/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>26/05/2026</v>
+        <v>09/07/2026</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -473,33 +473,33 @@
         <v>BOVINO</v>
       </c>
       <c r="I3" t="str">
-        <v>SAN NICANDRO GARGANICO</v>
+        <v>GERACI SICULO</v>
       </c>
       <c r="J3" t="str">
-        <v>FG</v>
+        <v>PA</v>
       </c>
       <c r="K3" t="str">
-        <v>PUGLIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>83594</v>
+        <v>83753</v>
       </c>
       <c r="B4" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C4" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D4" t="str">
-        <v>30/06/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="E4" t="str">
-        <v>02/03/2026</v>
+        <v>09/03/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>-</v>
+        <v>26/05/2026</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -508,18 +508,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I4" t="str">
-        <v>CARLENTINI</v>
+        <v>SAN NICANDRO GARGANICO</v>
       </c>
       <c r="J4" t="str">
-        <v>SR</v>
+        <v>FG</v>
       </c>
       <c r="K4" t="str">
-        <v>SICILIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>84474</v>
+        <v>84038</v>
       </c>
       <c r="B5" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -528,10 +528,10 @@
         <v>C</v>
       </c>
       <c r="D5" t="str">
-        <v>15/05/2026</v>
+        <v>07/01/2026</v>
       </c>
       <c r="E5" t="str">
-        <v>27/04/2026</v>
+        <v>07/01/2026</v>
       </c>
       <c r="F5" t="str">
         <v>-</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>84900</v>
+        <v>83896</v>
       </c>
       <c r="B6" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -563,10 +563,10 @@
         <v>C</v>
       </c>
       <c r="D6" t="str">
-        <v>27/05/2026</v>
+        <v>03/04/2026</v>
       </c>
       <c r="E6" t="str">
-        <v>27/05/2026</v>
+        <v>16/03/2026</v>
       </c>
       <c r="F6" t="str">
         <v>-</v>
@@ -578,18 +578,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I6" t="str">
-        <v>SANT\'AGATA DEL BIANCO</v>
+        <v>SAN NICANDRO GARGANICO</v>
       </c>
       <c r="J6" t="str">
-        <v>RC</v>
+        <v>FG</v>
       </c>
       <c r="K6" t="str">
-        <v>CALABRIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>83918</v>
+        <v>83181</v>
       </c>
       <c r="B7" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -598,10 +598,10 @@
         <v>C</v>
       </c>
       <c r="D7" t="str">
-        <v>26/05/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="E7" t="str">
-        <v>16/03/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="F7" t="str">
         <v>-</v>
@@ -610,13 +610,13 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>BOVINO</v>
+        <v>OVINO</v>
       </c>
       <c r="I7" t="str">
-        <v>GERACI SICULO</v>
+        <v>VILLAROSA</v>
       </c>
       <c r="J7" t="str">
-        <v>PA</v>
+        <v>EN</v>
       </c>
       <c r="K7" t="str">
         <v>SICILIA</v>
@@ -624,7 +624,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>83938</v>
+        <v>85040</v>
       </c>
       <c r="B8" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -633,10 +633,10 @@
         <v>C</v>
       </c>
       <c r="D8" t="str">
-        <v>26/05/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="E8" t="str">
-        <v>25/03/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="F8" t="str">
         <v>-</v>
@@ -648,18 +648,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I8" t="str">
-        <v>RANDAZZO</v>
+        <v>SAN NICANDRO GARGANICO</v>
       </c>
       <c r="J8" t="str">
-        <v>CT</v>
+        <v>FG</v>
       </c>
       <c r="K8" t="str">
-        <v>SICILIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>83548</v>
+        <v>83737</v>
       </c>
       <c r="B9" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -668,10 +668,10 @@
         <v>C</v>
       </c>
       <c r="D9" t="str">
-        <v>02/03/2026</v>
+        <v>26/03/2026</v>
       </c>
       <c r="E9" t="str">
-        <v>02/03/2026</v>
+        <v>03/03/2026</v>
       </c>
       <c r="F9" t="str">
         <v>-</v>
@@ -680,21 +680,21 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>OVINO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I9" t="str">
-        <v>RODI\' MILICI</v>
+        <v>SAN NICANDRO GARGANICO</v>
       </c>
       <c r="J9" t="str">
-        <v>ME</v>
+        <v>FG</v>
       </c>
       <c r="K9" t="str">
-        <v>SICILIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>83206</v>
+        <v>84900</v>
       </c>
       <c r="B10" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -703,10 +703,10 @@
         <v>C</v>
       </c>
       <c r="D10" t="str">
-        <v>24/04/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="E10" t="str">
-        <v>04/02/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="F10" t="str">
         <v>-</v>
@@ -718,45 +718,45 @@
         <v>BOVINO</v>
       </c>
       <c r="I10" t="str">
-        <v>PATTI</v>
+        <v>SANT\'AGATA DEL BIANCO</v>
       </c>
       <c r="J10" t="str">
-        <v>ME</v>
+        <v>RC</v>
       </c>
       <c r="K10" t="str">
-        <v>SICILIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>83267</v>
+        <v>83594</v>
       </c>
       <c r="B11" t="str">
-        <v>SIEROCONVERSIONE</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C11" t="str">
         <v>C</v>
       </c>
       <c r="D11" t="str">
-        <v>25/03/2026</v>
+        <v>30/06/2026</v>
       </c>
       <c r="E11" t="str">
-        <v>10/02/2026</v>
+        <v>02/03/2026</v>
       </c>
       <c r="F11" t="str">
         <v>-</v>
       </c>
       <c r="G11" t="str">
-        <v>B. abortus</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v>BOVINO</v>
       </c>
       <c r="I11" t="str">
-        <v>PATERNO\'</v>
+        <v>CARLENTINI</v>
       </c>
       <c r="J11" t="str">
-        <v>CT</v>
+        <v>SR</v>
       </c>
       <c r="K11" t="str">
         <v>SICILIA</v>
@@ -764,7 +764,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>83674</v>
+        <v>84474</v>
       </c>
       <c r="B12" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -773,10 +773,10 @@
         <v>C</v>
       </c>
       <c r="D12" t="str">
-        <v>18/06/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="E12" t="str">
-        <v>10/03/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="F12" t="str">
         <v>-</v>
@@ -788,18 +788,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I12" t="str">
-        <v>AUGUSTA</v>
+        <v>APRICENA</v>
       </c>
       <c r="J12" t="str">
-        <v>SR</v>
+        <v>FG</v>
       </c>
       <c r="K12" t="str">
-        <v>SICILIA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>84039</v>
+        <v>84465</v>
       </c>
       <c r="B13" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -808,22 +808,22 @@
         <v>C</v>
       </c>
       <c r="D13" t="str">
-        <v>18/05/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="E13" t="str">
-        <v>01/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="F13" t="str">
         <v>-</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>B. melitensis</v>
       </c>
       <c r="H13" t="str">
-        <v>BOVINO</v>
+        <v>OVINO</v>
       </c>
       <c r="I13" t="str">
-        <v>MESSINA</v>
+        <v>FIUMEDINISI</v>
       </c>
       <c r="J13" t="str">
         <v>ME</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>83548</v>
+        <v>83938</v>
       </c>
       <c r="B14" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -843,10 +843,10 @@
         <v>C</v>
       </c>
       <c r="D14" t="str">
-        <v>02/03/2026</v>
+        <v>26/05/2026</v>
       </c>
       <c r="E14" t="str">
-        <v>02/03/2026</v>
+        <v>25/03/2026</v>
       </c>
       <c r="F14" t="str">
         <v>-</v>
@@ -855,13 +855,13 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>CAPRA</v>
+        <v>BOVINO</v>
       </c>
       <c r="I14" t="str">
-        <v>RODI\' MILICI</v>
+        <v>RANDAZZO</v>
       </c>
       <c r="J14" t="str">
-        <v>ME</v>
+        <v>CT</v>
       </c>
       <c r="K14" t="str">
         <v>SICILIA</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>84512</v>
+        <v>83548</v>
       </c>
       <c r="B15" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -878,10 +878,10 @@
         <v>C</v>
       </c>
       <c r="D15" t="str">
-        <v>06/05/2026</v>
+        <v>02/03/2026</v>
       </c>
       <c r="E15" t="str">
-        <v>22/04/2026</v>
+        <v>02/03/2026</v>
       </c>
       <c r="F15" t="str">
         <v>-</v>
@@ -890,10 +890,10 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>CAPRA</v>
+        <v>OVINO</v>
       </c>
       <c r="I15" t="str">
-        <v>FONDACHELLI-FANTINA</v>
+        <v>RODI\' MILICI</v>
       </c>
       <c r="J15" t="str">
         <v>ME</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>83489</v>
+        <v>83206</v>
       </c>
       <c r="B16" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -913,10 +913,10 @@
         <v>C</v>
       </c>
       <c r="D16" t="str">
-        <v>08/05/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="E16" t="str">
-        <v>25/02/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="F16" t="str">
         <v>-</v>
@@ -928,10 +928,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I16" t="str">
-        <v>AGIRA</v>
+        <v>PATTI</v>
       </c>
       <c r="J16" t="str">
-        <v>EN</v>
+        <v>ME</v>
       </c>
       <c r="K16" t="str">
         <v>SICILIA</v>
@@ -939,42 +939,42 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>84038</v>
+        <v>83267</v>
       </c>
       <c r="B17" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>SIEROCONVERSIONE</v>
       </c>
       <c r="C17" t="str">
         <v>C</v>
       </c>
       <c r="D17" t="str">
-        <v>07/01/2026</v>
+        <v>25/03/2026</v>
       </c>
       <c r="E17" t="str">
-        <v>07/01/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="F17" t="str">
         <v>-</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>B. abortus</v>
       </c>
       <c r="H17" t="str">
-        <v>BUFALO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I17" t="str">
-        <v>APRICENA</v>
+        <v>PATERNO\'</v>
       </c>
       <c r="J17" t="str">
-        <v>FG</v>
+        <v>CT</v>
       </c>
       <c r="K17" t="str">
-        <v>PUGLIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>83085</v>
+        <v>83674</v>
       </c>
       <c r="B18" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -983,10 +983,10 @@
         <v>C</v>
       </c>
       <c r="D18" t="str">
-        <v>17/03/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="E18" t="str">
-        <v>23/01/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="F18" t="str">
         <v>-</v>
@@ -998,10 +998,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I18" t="str">
-        <v>AGIRA</v>
+        <v>AUGUSTA</v>
       </c>
       <c r="J18" t="str">
-        <v>EN</v>
+        <v>SR</v>
       </c>
       <c r="K18" t="str">
         <v>SICILIA</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>84992</v>
+        <v>84039</v>
       </c>
       <c r="B19" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1018,10 +1018,10 @@
         <v>C</v>
       </c>
       <c r="D19" t="str">
-        <v>05/06/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="E19" t="str">
-        <v>05/06/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="F19" t="str">
         <v>-</v>
@@ -1030,21 +1030,21 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>BUFALO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I19" t="str">
-        <v>CANCELLO ED ARNONE</v>
+        <v>MESSINA</v>
       </c>
       <c r="J19" t="str">
-        <v>CE</v>
+        <v>ME</v>
       </c>
       <c r="K19" t="str">
-        <v>CAMPANIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>83676</v>
+        <v>83548</v>
       </c>
       <c r="B20" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1053,10 +1053,10 @@
         <v>C</v>
       </c>
       <c r="D20" t="str">
-        <v>26/06/2026</v>
+        <v>02/03/2026</v>
       </c>
       <c r="E20" t="str">
-        <v>10/03/2026</v>
+        <v>02/03/2026</v>
       </c>
       <c r="F20" t="str">
         <v>-</v>
@@ -1065,13 +1065,13 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>BOVINO</v>
+        <v>CAPRA</v>
       </c>
       <c r="I20" t="str">
-        <v>BUCCHERI</v>
+        <v>RODI\' MILICI</v>
       </c>
       <c r="J20" t="str">
-        <v>SR</v>
+        <v>ME</v>
       </c>
       <c r="K20" t="str">
         <v>SICILIA</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>84268</v>
+        <v>84512</v>
       </c>
       <c r="B21" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1088,10 +1088,10 @@
         <v>C</v>
       </c>
       <c r="D21" t="str">
-        <v>14/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="E21" t="str">
-        <v>09/04/2026</v>
+        <v>22/04/2026</v>
       </c>
       <c r="F21" t="str">
         <v>-</v>
@@ -1100,21 +1100,21 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>BOVINO</v>
+        <v>CAPRA</v>
       </c>
       <c r="I21" t="str">
-        <v>SAN NICANDRO GARGANICO</v>
+        <v>FONDACHELLI-FANTINA</v>
       </c>
       <c r="J21" t="str">
-        <v>FG</v>
+        <v>ME</v>
       </c>
       <c r="K21" t="str">
-        <v>PUGLIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>84688</v>
+        <v>83489</v>
       </c>
       <c r="B22" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1123,10 +1123,10 @@
         <v>C</v>
       </c>
       <c r="D22" t="str">
-        <v>05/06/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="E22" t="str">
-        <v>12/05/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="F22" t="str">
         <v>-</v>
@@ -1138,18 +1138,18 @@
         <v>BOVINO</v>
       </c>
       <c r="I22" t="str">
-        <v>SAN NICANDRO GARGANICO</v>
+        <v>AGIRA</v>
       </c>
       <c r="J22" t="str">
-        <v>FG</v>
+        <v>EN</v>
       </c>
       <c r="K22" t="str">
-        <v>PUGLIA</v>
+        <v>SICILIA</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>84512</v>
+        <v>83675</v>
       </c>
       <c r="B23" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1158,10 +1158,10 @@
         <v>C</v>
       </c>
       <c r="D23" t="str">
-        <v>06/05/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E23" t="str">
-        <v>22/04/2026</v>
+        <v>27/02/2026</v>
       </c>
       <c r="F23" t="str">
         <v>-</v>
@@ -1170,13 +1170,13 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>OVINO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I23" t="str">
-        <v>FONDACHELLI-FANTINA</v>
+        <v>GANGI</v>
       </c>
       <c r="J23" t="str">
-        <v>ME</v>
+        <v>PA</v>
       </c>
       <c r="K23" t="str">
         <v>SICILIA</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>83870</v>
+        <v>84038</v>
       </c>
       <c r="B24" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1193,10 +1193,10 @@
         <v>C</v>
       </c>
       <c r="D24" t="str">
-        <v>04/05/2026</v>
+        <v>07/01/2026</v>
       </c>
       <c r="E24" t="str">
-        <v>13/03/2026</v>
+        <v>07/01/2026</v>
       </c>
       <c r="F24" t="str">
         <v>-</v>
@@ -1205,7 +1205,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>BOVINO</v>
+        <v>BUFALO</v>
       </c>
       <c r="I24" t="str">
         <v>APRICENA</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>83737</v>
+        <v>84992</v>
       </c>
       <c r="B25" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1228,10 +1228,10 @@
         <v>C</v>
       </c>
       <c r="D25" t="str">
-        <v>26/03/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="E25" t="str">
-        <v>03/03/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="F25" t="str">
         <v>-</v>
@@ -1240,21 +1240,21 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>BOVINO</v>
+        <v>BUFALO</v>
       </c>
       <c r="I25" t="str">
-        <v>SAN NICANDRO GARGANICO</v>
+        <v>CANCELLO ED ARNONE</v>
       </c>
       <c r="J25" t="str">
-        <v>FG</v>
+        <v>CE</v>
       </c>
       <c r="K25" t="str">
-        <v>PUGLIA</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>84465</v>
+        <v>83676</v>
       </c>
       <c r="B26" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1263,25 +1263,25 @@
         <v>C</v>
       </c>
       <c r="D26" t="str">
-        <v>11/06/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="E26" t="str">
-        <v>30/04/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="F26" t="str">
         <v>-</v>
       </c>
       <c r="G26" t="str">
-        <v>B. melitensis</v>
+        <v/>
       </c>
       <c r="H26" t="str">
-        <v>OVINO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I26" t="str">
-        <v>FIUMEDINISI</v>
+        <v>BUCCHERI</v>
       </c>
       <c r="J26" t="str">
-        <v>ME</v>
+        <v>SR</v>
       </c>
       <c r="K26" t="str">
         <v>SICILIA</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>83181</v>
+        <v>85498</v>
       </c>
       <c r="B27" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1298,10 +1298,10 @@
         <v>C</v>
       </c>
       <c r="D27" t="str">
-        <v>19/03/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="E27" t="str">
-        <v>02/02/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="F27" t="str">
         <v>-</v>
@@ -1310,10 +1310,10 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>OVINO</v>
+        <v>BOVINO</v>
       </c>
       <c r="I27" t="str">
-        <v>VILLAROSA</v>
+        <v>CENTURIPE</v>
       </c>
       <c r="J27" t="str">
         <v>EN</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>84038</v>
+        <v>84268</v>
       </c>
       <c r="B28" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1333,10 +1333,10 @@
         <v>C</v>
       </c>
       <c r="D28" t="str">
-        <v>07/01/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="E28" t="str">
-        <v>07/01/2026</v>
+        <v>09/04/2026</v>
       </c>
       <c r="F28" t="str">
         <v>-</v>
@@ -1348,7 +1348,7 @@
         <v>BOVINO</v>
       </c>
       <c r="I28" t="str">
-        <v>APRICENA</v>
+        <v>SAN NICANDRO GARGANICO</v>
       </c>
       <c r="J28" t="str">
         <v>FG</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>83896</v>
+        <v>84688</v>
       </c>
       <c r="B29" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1368,10 +1368,10 @@
         <v>C</v>
       </c>
       <c r="D29" t="str">
-        <v>03/04/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="E29" t="str">
-        <v>16/03/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="F29" t="str">
         <v>-</v>
@@ -1392,9 +1392,114 @@
         <v>PUGLIA</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30">
+        <v>83085</v>
+      </c>
+      <c r="B30" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C30" t="str">
+        <v>C</v>
+      </c>
+      <c r="D30" t="str">
+        <v>17/03/2026</v>
+      </c>
+      <c r="E30" t="str">
+        <v>23/01/2026</v>
+      </c>
+      <c r="F30" t="str">
+        <v>-</v>
+      </c>
+      <c r="G30" t="str">
+        <v>B. abortus</v>
+      </c>
+      <c r="H30" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I30" t="str">
+        <v>AGIRA</v>
+      </c>
+      <c r="J30" t="str">
+        <v>EN</v>
+      </c>
+      <c r="K30" t="str">
+        <v>SICILIA</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>84512</v>
+      </c>
+      <c r="B31" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C31" t="str">
+        <v>C</v>
+      </c>
+      <c r="D31" t="str">
+        <v>06/05/2026</v>
+      </c>
+      <c r="E31" t="str">
+        <v>22/04/2026</v>
+      </c>
+      <c r="F31" t="str">
+        <v>-</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>OVINO</v>
+      </c>
+      <c r="I31" t="str">
+        <v>FONDACHELLI-FANTINA</v>
+      </c>
+      <c r="J31" t="str">
+        <v>ME</v>
+      </c>
+      <c r="K31" t="str">
+        <v>SICILIA</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>83870</v>
+      </c>
+      <c r="B32" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C32" t="str">
+        <v>C</v>
+      </c>
+      <c r="D32" t="str">
+        <v>04/05/2026</v>
+      </c>
+      <c r="E32" t="str">
+        <v>13/03/2026</v>
+      </c>
+      <c r="F32" t="str">
+        <v>-</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I32" t="str">
+        <v>APRICENA</v>
+      </c>
+      <c r="J32" t="str">
+        <v>FG</v>
+      </c>
+      <c r="K32" t="str">
+        <v>PUGLIA</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K32"/>
   </ignoredErrors>
 </worksheet>
 </file>